--- a/entertainment_forms/006_letter_to_santa_template--entertainment_forms.xlsx
+++ b/entertainment_forms/006_letter_to_santa_template--entertainment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
     <col width="35" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -525,20 +525,20 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>What's your name</t>
+          <t>What's your name?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -554,7 +554,7 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Why should I get it?</t>
+          <t>Why do you want this toy?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -604,14 +604,14 @@
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -621,13 +621,13 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Do you have any other questions for Santa?</t>
+          <t>How old are you?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -644,20 +644,20 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>What's your favorite season?</t>
+          <t>Do you want to share this letter with Santa?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -667,20 +667,20 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>What's your favorite color?</t>
+          <t>What's the best part about being a kid?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>What's your favorite animal?</t>
+          <t>Do you have any other questions for Santa?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -703,7 +703,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -713,13 +713,13 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>What is your favorite food?</t>
+          <t>Where are you from?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Where are you from?</t>
+          <t>Who is helping you write this letter?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -749,7 +749,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -759,20 +759,20 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Who is helping you write this letter?</t>
+          <t>What's your favorite color?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -782,312 +782,13 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>How old are you?</t>
+          <t>What's your favorite animal?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>letter_to_santa_template_page_13</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Do you want to send it to me?</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>letter_to_santa_template_page_14</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>What's the best thing about being a kid?</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>letter_to_santa_template_page_15</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>letter_to_santa_template_page_16</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>letter_to_santa_template_page_17</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>letter_to_santa_template_page_18</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>letter_to_santa_template_page_19</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>letter_to_santa_template_page_20</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>letter_to_santa_template_page_21</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>letter_to_santa_template_page_22</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>letter_to_santa_template_page_23</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>letter_to_santa_template_page_24</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>letter_to_santa_template_page_25</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
         </is>
       </c>
     </row>
@@ -1102,12 +803,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1130,34 +831,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>letter_to_santa_template_page_2_choices</t>
+          <t>letter_to_santa_template_page_4_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>playing_outside</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Playing outside</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>letter_to_santa_template_page_2_choices</t>
+          <t>letter_to_santa_template_page_4_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>reading_books</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Reading books</t>
         </is>
       </c>
     </row>
@@ -1169,12 +870,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>playing_with_friends</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Playing with friends</t>
         </is>
       </c>
     </row>
@@ -1186,46 +887,46 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>playing_video_games</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Playing video games</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>letter_to_santa_template_page_5_choices</t>
+          <t>letter_to_santa_template_page_4_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>letter_to_santa_template_page_5_choices</t>
+          <t>letter_to_santa_template_page_6_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1237,29 +938,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>letter_to_santa_template_page_6_choices</t>
+          <t>letter_to_santa_template_page_7_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>playing_with_friends</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Playing with friends</t>
         </is>
       </c>
     </row>
@@ -1271,12 +972,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>getting_presents!</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Getting presents!</t>
         </is>
       </c>
     </row>
@@ -1288,148 +989,216 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>riding_a_bike</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Riding a bike</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>letter_to_santa_template_page_8_choices</t>
+          <t>letter_to_santa_template_page_7_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>playing_outside</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Playing outside</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>letter_to_santa_template_page_8_choices</t>
+          <t>letter_to_santa_template_page_7_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>eating_cookies</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Eating cookies</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>letter_to_santa_template_page_9_choices</t>
+          <t>letter_to_santa_template_page_11_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>blue</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Blue</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>letter_to_santa_template_page_9_choices</t>
+          <t>letter_to_santa_template_page_11_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>red</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Red</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>letter_to_santa_template_page_13_choices</t>
+          <t>letter_to_santa_template_page_11_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>green</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Green</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>letter_to_santa_template_page_13_choices</t>
+          <t>letter_to_santa_template_page_11_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yellow</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yellow</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>letter_to_santa_template_page_14_choices</t>
+          <t>letter_to_santa_template_page_11_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>purple</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Purple</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>letter_to_santa_template_page_14_choices</t>
+          <t>letter_to_santa_template_page_12_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Dog</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>letter_to_santa_template_page_12_choices</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>cat</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Cat</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>letter_to_santa_template_page_12_choices</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>bear</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Bear</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>letter_to_santa_template_page_12_choices</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>bird</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Bird</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>letter_to_santa_template_page_12_choices</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>other_(please_specify)</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
